--- a/dcf/LLY.xlsx
+++ b/dcf/LLY.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1126,25 @@
         <v>15</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>976.1223219493659</v>
+        <v>861.1362476426165</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>934.8355447401905</v>
+        <v>824.9198436773171</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>895.5407951619378</v>
+        <v>790.4451285526801</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>858.1312044424794</v>
+        <v>757.6187952907064</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>822.506151326454</v>
+        <v>726.3529876384375</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>788.5708683643771</v>
+        <v>696.5649567151879</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>756.2360747524464</v>
+        <v>668.1767408083015</v>
       </c>
     </row>
     <row r="6">
@@ -1152,25 +1152,25 @@
         <v>16</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>1022.943972938888</v>
+        <v>901.9257505781883</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>979.4831969406792</v>
+        <v>863.8154294161827</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>938.1249698203135</v>
+        <v>827.5430796186391</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>898.7563216598168</v>
+        <v>793.0100790872845</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>861.2708932522797</v>
+        <v>760.1235728519744</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>825.5685192137985</v>
+        <v>728.7961095267245</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>791.5548392235877</v>
+        <v>698.9453022885184</v>
       </c>
     </row>
     <row r="7">
@@ -1178,129 +1178,129 @@
         <v>17</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>1069.765623928411</v>
+        <v>942.7152535137599</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>1024.130849141168</v>
+        <v>902.7110151550486</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>980.7091444786889</v>
+        <v>864.641030684598</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>939.381438877154</v>
+        <v>828.4013628838626</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>900.0356351781054</v>
+        <v>793.8941580655111</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>862.5661700632201</v>
+        <v>761.0272623382612</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>826.8736036947289</v>
+        <v>729.7138637687352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
         <v>18</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>1116.587274917933</v>
+      <c r="B8" s="53" t="n">
+        <v>983.5047564493317</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>1068.778501341657</v>
+        <v>941.6066008939144</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>1023.293319137065</v>
+        <v>901.7389817505568</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>980.0065560944914</v>
+        <v>863.792646680441</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>938.8003771039311</v>
+        <v>827.6647432790478</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>899.5638209126414</v>
+        <v>793.2584151497977</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>862.1923681658702</v>
+        <v>760.4824252489522</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>19</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>1163.408925907456</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>1113.426153542146</v>
+      <c r="B9" s="53" t="n">
+        <v>1024.294259384903</v>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>980.5021866327801</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>1065.87749379544</v>
+        <v>938.8369328165156</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>1020.631673311829</v>
+        <v>899.1839304770189</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>977.5651190297567</v>
+        <v>861.4353284925845</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>936.561471762063</v>
+        <v>825.4895679613342</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>897.5111326370114</v>
+        <v>791.2509867291691</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>20</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>1210.230576896978</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>1158.073805742635</v>
+      <c r="B10" s="53" t="n">
+        <v>1065.083762320475</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>1019.397772371646</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>1108.461668453816</v>
+        <v>975.9348838824747</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>1061.256790529166</v>
+        <v>934.575214273597</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>1016.329860955582</v>
+        <v>895.2059137061212</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>973.5591226114842</v>
+        <v>857.7207207728709</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>932.8298971081527</v>
+        <v>822.019548209386</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
         <v>21</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>1257.052227886501</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>1202.721457943123</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>1151.045843112191</v>
+      <c r="B11" s="53" t="n">
+        <v>1105.873265256047</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <v>1058.293358110512</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>1013.032834948433</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>1101.881907746503</v>
+        <v>969.9664980701751</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>1055.094602881408</v>
+        <v>928.976498919658</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>1010.556773460906</v>
+        <v>889.9518735844075</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>968.148661579294</v>
+        <v>852.7881096896031</v>
       </c>
     </row>
     <row r="13">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9528741444216118</v>
+        <v>0.9538930306959708</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24567,13 +24567,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>980.0065560944914</v>
+        <v>863.792646680441</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>1322.593260889294</v>
+        <v>1138.276751549099</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>717.3047143655083</v>
+        <v>647.7523921615875</v>
       </c>
     </row>
     <row r="59">
